--- a/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,19 @@
     <t>SOLANO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MENA</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>ANGELES</t>
+  </si>
+  <si>
+    <t>JARET</t>
   </si>
 </sst>
 </file>
@@ -477,7 +486,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -486,10 +495,10 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -568,19 +577,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.48999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -594,16 +606,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.97</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -653,22 +668,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,10 +757,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -755,6 +770,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920357</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,10 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MENA</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>ANGELES</t>
-  </si>
-  <si>
-    <t>JARET</t>
   </si>
 </sst>
 </file>
@@ -674,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>80.48999999999999</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,10 +748,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -770,29 +761,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920357</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
@@ -674,7 +674,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,7 +700,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20231.xlsx
@@ -674,7 +674,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,7 +700,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
